--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_M30B5_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_M30B5_IN_Piura.xlsx
@@ -1804,7 +1804,7 @@
       </c>
       <c r="C10" s="19">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>28.44</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="C11" s="30">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>38.53</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="C12" s="19">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>32.32</v>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="C13" s="21">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>0.71</v>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
@@ -1921,11 +1921,11 @@
       </c>
       <c r="B15" s="45">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>90.9035</v>
       </c>
       <c r="C15" s="46">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D15" s="44" t="inlineStr">
         <is>
@@ -1946,11 +1946,11 @@
       </c>
       <c r="B16" s="48">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>60.877</v>
       </c>
       <c r="C16" s="49">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>66.97</v>
       </c>
       <c r="D16" s="47" t="inlineStr">
         <is>
@@ -1971,11 +1971,11 @@
       </c>
       <c r="B17" s="48">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>30.0265</v>
       </c>
       <c r="C17" s="49">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>33.03</v>
       </c>
       <c r="D17" s="47" t="inlineStr">
         <is>
@@ -2150,11 +2150,11 @@
       </c>
       <c r="B28" s="22">
         <f>SUM(B25:B27)</f>
-        <v/>
+        <v>90.9218</v>
       </c>
       <c r="C28" s="23">
         <f>SUM(C25:C27)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D28" s="17" t="inlineStr"/>
       <c r="E28" s="17" t="inlineStr"/>
@@ -2273,6 +2273,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2539,6 +2540,7 @@
       <c r="F17" s="17" t="inlineStr"/>
       <c r="G17" s="17" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
@@ -2583,6 +2585,7 @@
       <c r="G20" s="8" t="n"/>
       <c r="H20" s="8" t="n"/>
     </row>
+    <row r="21"/>
     <row r="22" ht="156" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
@@ -3066,11 +3069,11 @@
       </c>
       <c r="B20" s="33">
         <f>SUM(B10:B19)</f>
-        <v/>
+        <v>552.18</v>
       </c>
       <c r="C20" s="23">
         <f>SUM(C10:C19)</f>
-        <v/>
+        <v>99.98</v>
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
@@ -3080,19 +3083,19 @@
       <c r="E20" s="17" t="inlineStr"/>
       <c r="F20" s="17">
         <f>ROUND(AVERAGE(F10:F19),2)</f>
-        <v/>
+        <v>29.09</v>
       </c>
       <c r="G20" s="22">
         <f>ROUND(AVERAGE(G10:G19),4)</f>
-        <v/>
+        <v>0.6292</v>
       </c>
       <c r="H20" s="23">
         <f>ROUND(AVERAGE(H10:H19),2)</f>
-        <v/>
+        <v>93.19</v>
       </c>
       <c r="I20" s="23">
         <f>ROUND(AVERAGE(I10:I19),2)</f>
-        <v/>
+        <v>9.85</v>
       </c>
     </row>
     <row r="21"/>
